--- a/database/seeders/data.xlsx
+++ b/database/seeders/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\daarulhuda\database\seeders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC3FBBBB-D7ED-42B1-B1AD-68130A905632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D92E36E-96D8-4D43-9B71-44425C8C9DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9DF597BA-00D5-47EB-A950-FD6885C82779}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="126">
   <si>
     <t>3175102301230012</t>
   </si>
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t>entry_year</t>
+  </si>
+  <si>
+    <t>nisn</t>
   </si>
 </sst>
 </file>
@@ -816,7 +819,7 @@
         <v>120</v>
       </c>
       <c r="B1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C1" t="s">
         <v>121</v>
